--- a/public/tmfit-workout-template.xlsx
+++ b/public/tmfit-workout-template.xlsx
@@ -2,9 +2,9 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" r:id="R2089b46a5f804040"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHEDA" sheetId="2" r:id="Rf091cf04a59846bd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANCA DATI" sheetId="3" r:id="R3d3b899d30894090"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CONFIG" sheetId="1" r:id="Ra953a398424e4bd2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="SCHEDA" sheetId="2" r:id="Rf07cac6ee9934885"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BANCA DATI" sheetId="3" r:id="Re8dc2b05ccf843b6"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -15,7 +15,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="9">
+  <x:fonts count="10">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -67,8 +67,13 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -100,6 +105,11 @@
         <x:fgColor rgb="FFFBFEFF"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF07111F"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border/>
@@ -108,7 +118,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="65">
+  <x:cellXfs count="70">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -261,6 +271,17 @@
     <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -472,7 +493,7 @@
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
       <x:c r="A1" s="29" t="str">
-        <x:v>TMFIT · TEMPLATE ALLENAMENTO</x:v>
+        <x:v>TMFIT · TEMPLATE ALLENAMENTO v5.4.1</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str"/>
       <x:c r="C1" s="29" t="str"/>
@@ -527,7 +548,7 @@
       </x:c>
       <x:c r="C6" s="33" t="str"/>
       <x:c r="D6" s="22" t="str">
-        <x:v>3. SERIE/RIP FISSE: esempi 3x8-10, 1x5 + 3x8-10, 2x12-15/LATO, 15 MIN.</x:v>
+        <x:v>3. PRESCRIZIONE BASE: usa 3x8-10 oppure 1x5 + 3x8-10. L'app mantiene la scrittura compatta.</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="24" customHeight="1">
@@ -537,7 +558,7 @@
       <x:c r="B7" s="32" t="str"/>
       <x:c r="C7" s="33" t="str"/>
       <x:c r="D7" s="22" t="str">
-        <x:v>4. Se usi progressioni, compila SETT. 1 fino alla durata del programma. Una settimana vuota viene segnalata come mancante.</x:v>
+        <x:v>4. Nelle colonne SETT. usa la stessa sintassi: es. 1x5 + 3x8, 3x10, 2x12-15/LATO.</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="24" customHeight="1">
@@ -565,7 +586,7 @@
       <x:c r="B10" s="33" t="str"/>
       <x:c r="C10" s="33" t="str"/>
       <x:c r="D10" s="22" t="str">
-        <x:v>7. Puoi lasciare vuote le colonne SETT. se la prescrizione è fissa.</x:v>
+        <x:v>7. Compila SETT. 1 fino alla durata reale. Le settimane non definite possono restare vuote.</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="24" customHeight="1">
@@ -573,7 +594,51 @@
       <x:c r="B11" s="33" t="str"/>
       <x:c r="C11" s="33" t="str"/>
       <x:c r="D11" s="22" t="str">
-        <x:v>8. Non spostare le colonne base; puoi comunque aggiungere note nella colonna Modalità esecuzione.</x:v>
+        <x:v>8. Non modificare i nomi dei fogli CONFIG, SCHEDA e BANCA DATI.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="68" t="str">
+        <x:v>ESEMPI PRESCRIZIONE</x:v>
+      </x:c>
+      <x:c r="B13" s="68"/>
+      <x:c r="C13" s="68"/>
+      <x:c r="D13" s="68"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="33" t="str">
+        <x:v>Semplice</x:v>
+      </x:c>
+      <x:c r="B14" s="69" t="str">
+        <x:v>3x8-10</x:v>
+      </x:c>
+      <x:c r="C14" s="33"/>
+      <x:c r="D14" s="33" t="str">
+        <x:v>3 serie da 8-10</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="33" t="str">
+        <x:v>Top + back-off</x:v>
+      </x:c>
+      <x:c r="B15" s="69" t="str">
+        <x:v>1x5 + 3x8</x:v>
+      </x:c>
+      <x:c r="C15" s="33"/>
+      <x:c r="D15" s="33" t="str">
+        <x:v>1 serie da 5 + 3 serie da 8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="33" t="str">
+        <x:v>Tempo / lato</x:v>
+      </x:c>
+      <x:c r="B16" s="69" t="str">
+        <x:v>3x30 sec oppure 2x12-15/LATO</x:v>
+      </x:c>
+      <x:c r="C16" s="33"/>
+      <x:c r="D16" s="33" t="str">
+        <x:v>Formati accettati</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -703,7 +768,7 @@
         <x:v>ESERCIZIO</x:v>
       </x:c>
       <x:c r="B5" s="50" t="str">
-        <x:v>SERIE/RIP FISSE</x:v>
+        <x:v>PRESCRIZIONE BASE</x:v>
       </x:c>
       <x:c r="C5" s="50" t="str">
         <x:v>RECUPERO</x:v>
@@ -1024,7 +1089,7 @@
         <x:v>ESERCIZIO</x:v>
       </x:c>
       <x:c r="B20" s="50" t="str">
-        <x:v>SERIE/RIP FISSE</x:v>
+        <x:v>PRESCRIZIONE BASE</x:v>
       </x:c>
       <x:c r="C20" s="50" t="str">
         <x:v>RECUPERO</x:v>
@@ -1345,7 +1410,7 @@
         <x:v>ESERCIZIO</x:v>
       </x:c>
       <x:c r="B35" s="50" t="str">
-        <x:v>SERIE/RIP FISSE</x:v>
+        <x:v>PRESCRIZIONE BASE</x:v>
       </x:c>
       <x:c r="C35" s="50" t="str">
         <x:v>RECUPERO</x:v>
@@ -1666,7 +1731,7 @@
         <x:v>ESERCIZIO</x:v>
       </x:c>
       <x:c r="B50" s="50" t="str">
-        <x:v>SERIE/RIP FISSE</x:v>
+        <x:v>PRESCRIZIONE BASE</x:v>
       </x:c>
       <x:c r="C50" s="50" t="str">
         <x:v>RECUPERO</x:v>
@@ -1987,7 +2052,7 @@
         <x:v>ESERCIZIO</x:v>
       </x:c>
       <x:c r="B65" s="50" t="str">
-        <x:v>SERIE/RIP FISSE</x:v>
+        <x:v>PRESCRIZIONE BASE</x:v>
       </x:c>
       <x:c r="C65" s="50" t="str">
         <x:v>RECUPERO</x:v>
@@ -2308,7 +2373,7 @@
         <x:v>ESERCIZIO</x:v>
       </x:c>
       <x:c r="B80" s="50" t="str">
-        <x:v>SERIE/RIP FISSE</x:v>
+        <x:v>PRESCRIZIONE BASE</x:v>
       </x:c>
       <x:c r="C80" s="50" t="str">
         <x:v>RECUPERO</x:v>
